--- a/epad_inkl_11_kr.xlsx
+++ b/epad_inkl_11_kr.xlsx
@@ -408,414 +408,25 @@
         </is>
       </c>
       <c r="C2">
-        <v>624.3198500000001</v>
+        <v>585.2427500000001</v>
       </c>
       <c r="D2">
-        <v>670.65185</v>
+        <v>628.6227500000001</v>
       </c>
       <c r="E2">
-        <v>381.07685</v>
+        <v>357.4977500000001</v>
       </c>
       <c r="F2">
-        <v>226.09631</v>
+        <v>212.3916500000001</v>
       </c>
       <c r="G2">
-        <v>557.7176000000001</v>
+        <v>522.884</v>
       </c>
       <c r="H2">
-        <v>480.11535</v>
+        <v>449.5252500000001</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Word-dokument" ma:contentTypeID="0x010100098B676CC530A34A9FB1F4ACAD0C0A17" ma:contentTypeVersion="35" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="32bac50741fd7a29ba3d71556f388968">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="caf9241f-7654-46e4-b38c-0683f7584438" xmlns:ns3="08670d86-fc33-4f61-bf51-96e019343c8b" xmlns:ns4="286bd567-8383-458b-8b10-610e1dbf4dce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e3bdb6b18078f058c2f3788d7e990f1a" ns2:_="" ns3:_="" ns4:_="">
-    <xsd:import namespace="caf9241f-7654-46e4-b38c-0683f7584438"/>
-    <xsd:import namespace="08670d86-fc33-4f61-bf51-96e019343c8b"/>
-    <xsd:import namespace="286bd567-8383-458b-8b10-610e1dbf4dce"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:Prosess" minOccurs="0"/>
-                <xsd:element ref="ns2:Vedtattdato" minOccurs="0"/>
-                <xsd:element ref="ns2:Slette_x003f_" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAllLabel" minOccurs="0"/>
-                <xsd:element ref="ns3:n3e020d9d98c48dbb65f924b9bc22a2a" minOccurs="0"/>
-                <xsd:element ref="ns3:g98ade60b1a5493f9b7127fdb0eec544" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns4:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns4:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:fb87f3f3a1014cb4ad0ec65499e03bb4" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:h5401ff79c16481cab8da1bb26f238ab" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="caf9241f-7654-46e4-b38c-0683f7584438" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="Prosess" ma:index="3" nillable="true" ma:displayName="Prosess" ma:format="Dropdown" ma:indexed="true" ma:internalName="Prosess" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Tidligere relevante arbeider"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Vedtattdato" ma:index="4" nillable="true" ma:displayName="Vedtatt dato" ma:default="2021-03-02T00:00:00Z" ma:description="Dato for KT-møte dokumentet ble besluttet ferdig." ma:format="DateOnly" ma:internalName="Vedtattdato" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Slette_x003f_" ma:index="5" nillable="true" ma:displayName="Slette?" ma:format="Dropdown" ma:internalName="Slette_x003f_" ma:readOnly="false">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoice">
-            <xsd:sequence>
-              <xsd:element name="Value" maxOccurs="unbounded" minOccurs="0" nillable="true">
-                <xsd:simpleType>
-                  <xsd:restriction base="dms:Choice">
-                    <xsd:enumeration value="Ja"/>
-                    <xsd:enumeration value="Nei"/>
-                    <xsd:enumeration value="Usikker"/>
-                  </xsd:restriction>
-                </xsd:simpleType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildemerkelapper" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="64152832-9f03-4628-8f8a-984f7e09cd82" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="24" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="27" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="28" nillable="true" ma:displayName="KeyPoints" ma:hidden="true" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="29" nillable="true" ma:displayName="Tags" ma:hidden="true" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="30" nillable="true" ma:displayName="Extracted Text" ma:hidden="true" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="31" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="fb87f3f3a1014cb4ad0ec65499e03bb4" ma:index="34" nillable="true" ma:taxonomy="true" ma:internalName="fb87f3f3a1014cb4ad0ec65499e03bb4" ma:taxonomyFieldName="Fagtema0" ma:displayName="Fagtema" ma:readOnly="false" ma:default="" ma:fieldId="{fb87f3f3-a101-4cb4-ad0e-c65499e03bb4}" ma:taxonomyMulti="true" ma:sspId="64152832-9f03-4628-8f8a-984f7e09cd82" ma:termSetId="eaf1a95a-330f-4713-ba0b-64ad2524e953" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="35" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="h5401ff79c16481cab8da1bb26f238ab" ma:index="37" nillable="true" ma:taxonomy="true" ma:internalName="h5401ff79c16481cab8da1bb26f238ab" ma:taxonomyFieldName="Dokumenttype_termsett" ma:displayName="Dokumenttype Termsett" ma:readOnly="false" ma:default="" ma:fieldId="{15401ff7-9c16-481c-ab8d-a1bb26f238ab}" ma:taxonomyMulti="true" ma:sspId="64152832-9f03-4628-8f8a-984f7e09cd82" ma:termSetId="65749bcf-2538-4e87-b139-ae273a755232" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="08670d86-fc33-4f61-bf51-96e019343c8b" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAllLabel" ma:index="9" nillable="true" ma:displayName="Taxonomy Catch All Column1" ma:hidden="true" ma:list="{9a588cb2-5654-4e11-92e8-3f1cc2e35934}" ma:internalName="TaxCatchAllLabel" ma:readOnly="false" ma:showField="CatchAllDataLabel" ma:web="286bd567-8383-458b-8b10-610e1dbf4dce">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="n3e020d9d98c48dbb65f924b9bc22a2a" ma:index="10" nillable="true" ma:taxonomy="true" ma:internalName="n3e020d9d98c48dbb65f924b9bc22a2a" ma:taxonomyFieldName="NVE_Tema" ma:displayName="NVE tema" ma:readOnly="false" ma:default="" ma:fieldId="{73e020d9-d98c-48db-b65f-924b9bc22a2a}" ma:taxonomyMulti="true" ma:sspId="64152832-9f03-4628-8f8a-984f7e09cd82" ma:termSetId="8e6ad744-58b5-4dbb-88a2-80de7c4ff1df" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="g98ade60b1a5493f9b7127fdb0eec544" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="g98ade60b1a5493f9b7127fdb0eec544" ma:taxonomyFieldName="NVE_Dokumenttype" ma:displayName="Dokumenttype NVE" ma:readOnly="false" ma:default="" ma:fieldId="{098ade60-b1a5-493f-9b71-27fdb0eec544}" ma:sspId="64152832-9f03-4628-8f8a-984f7e09cd82" ma:termSetId="7a928a34-8131-48a8-82d2-76c63c72cabe" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{9a588cb2-5654-4e11-92e8-3f1cc2e35934}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="286bd567-8383-458b-8b10-610e1dbf4dce">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="286bd567-8383-458b-8b10-610e1dbf4dce" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Delt med" ma:hidden="true" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Delingsdetaljer" ma:hidden="true" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:displayName="Innholdstype"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:displayName="Tittel"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="64152832-9f03-4628-8f8a-984f7e09cd82" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Vedtattdato xmlns="caf9241f-7654-46e4-b38c-0683f7584438">2021-03-02T00:00:00+00:00</Vedtattdato>
-    <Slette_x003f_ xmlns="caf9241f-7654-46e4-b38c-0683f7584438" xsi:nil="true"/>
-    <Prosess xmlns="caf9241f-7654-46e4-b38c-0683f7584438" xsi:nil="true"/>
-    <fb87f3f3a1014cb4ad0ec65499e03bb4 xmlns="caf9241f-7654-46e4-b38c-0683f7584438">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </fb87f3f3a1014cb4ad0ec65499e03bb4>
-    <n3e020d9d98c48dbb65f924b9bc22a2a xmlns="08670d86-fc33-4f61-bf51-96e019343c8b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </n3e020d9d98c48dbb65f924b9bc22a2a>
-    <TaxCatchAllLabel xmlns="08670d86-fc33-4f61-bf51-96e019343c8b" xsi:nil="true"/>
-    <h5401ff79c16481cab8da1bb26f238ab xmlns="caf9241f-7654-46e4-b38c-0683f7584438">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </h5401ff79c16481cab8da1bb26f238ab>
-    <g98ade60b1a5493f9b7127fdb0eec544 xmlns="08670d86-fc33-4f61-bf51-96e019343c8b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </g98ade60b1a5493f9b7127fdb0eec544>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="caf9241f-7654-46e4-b38c-0683f7584438">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="08670d86-fc33-4f61-bf51-96e019343c8b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52EEF393-B3FB-452D-A16B-A27EAABDD18E}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E6058D8-DB9A-4833-AF2E-7DBEA400682C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{327DC593-E2C9-4E1B-92D0-5F1F5AF4DFD9}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5459C719-030B-49F2-A601-332F69459B1E}"/>
 </file>